--- a/ejemplos/Calcular_alturas_Espana.xlsx
+++ b/ejemplos/Calcular_alturas_Espana.xlsx
@@ -5,11 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Parcelas" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="PiesMayores" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Parcelas" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="PiesMayores" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Metadatos" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Códigos especies" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Códigos provincias" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="270">
   <si>
     <t xml:space="preserve">ID_Inventario</t>
   </si>
@@ -29,6 +32,9 @@
     <t xml:space="preserve">ID_Parcela</t>
   </si>
   <si>
+    <t xml:space="preserve">Provincia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Region_biogeografica</t>
   </si>
   <si>
@@ -38,6 +44,12 @@
     <t xml:space="preserve">Origen_masa</t>
   </si>
   <si>
+    <t xml:space="preserve">Anho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alpina</t>
   </si>
   <si>
@@ -75,15 +87,763 @@
   </si>
   <si>
     <t xml:space="preserve">altura_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CÓDIGO DE COLORES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIGNIFICADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARIABLES PARCELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIPO DATO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPLICACIÓN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROJO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">campo obligatorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cadena texto / numérico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código identificador único de inventario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NARANJA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">si está disponible mejor, sino será calculado o tomará un valor por defecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código identificador único de cada parcela perteneciente al inventario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">información de ayuda disponible en este documento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">numérico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código de provincia en la que se ubica la parcela de acuerdo con el INE; si está presente se puede calcular el volumen con corteza, v. sin corteza. v. leñas e incremento annual de acuerdo a los modelos del IFN. Consulta los códigos en la hoja “Códigos provincias”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cadena texto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Región biogeográfica donde se encuentra el monte. Las opciones son  "Alpina", "Atlántica", "Macaronésica" y "Mediterránea", siendo “Mediterránea” la opción por defecto. Este campo es necesario únicamente para calcular la altura inicial de cada árbol si no está disponible en el inventario. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A continuación tienes la explicación de las variables de las hojas "Parcelas"  (derecha) y "PiesMayores"  (derecha-abajo), que deberás cubrir con tus datos para utilizarlos en SIMANFOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selección del origen de la masa entre "natural" o "plantación", siendo “natural” la opción por defecto. Este campo es necesario únicamente para calcular la altura inicial de cada árbol si no está disponible en el inventario. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Este campo es necesario únicamente para calcular la altura inicial de cada árbol si no está disponible en el inventario. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Año en el que fue realizado el inventario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADVERTENCIA: no cambies el nombre de ningún encabezado ni lo borres, si no tienes que cubrirlo déjalo vacío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edad promedio de la masa (años)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARIABLES ÁRBOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código identificador único de cada árbol perteneciente a una parcela del inventario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código de especie, siguiendo la codificación del Inventario Forestal Nacional de España. Consulta los códigos en la hoja “Códigos especies”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factor de expansión. Representa la cantidad de árboles en una hectárea de superficie a los que equivale el árbol medido. Se calcula como un cociente de superficies: 1ha/(superficie parcela); por ejemplo, factor_expansion=(10000m2)/(1000m2)=10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diámetro medido a la altura del pecho (diámetro normal) (cm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Altura total del árbol (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código especie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre científico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heberdenia bahamensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acacia spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phillyrea latifolia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ailanthus altissima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malus sylvestris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celtis australis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taxus baccata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crataegus spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pyrus spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cedrus atlantica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamaecyparis lawsoniana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otras coniferas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinus sylvestris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinus uncinata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinus pinea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinus halepensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinus nigra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinus pinaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinus canariensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinus radiata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otros pinos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abies alba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abies pinsapo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Picea abies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pseudotsuga menziesii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larix spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cupressus sempervirens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juniperus communis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juniperus thurifera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juniperus phoenicea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quercus robur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quercus petraea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quercus pyrenaica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quercus faginea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quercus ilex ssp. ballota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quercus suber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quercus canariensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quercus rubra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otros quercus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Populus alba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Populus tremula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamarix spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alnus glutinosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraxinus angustifolia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulmus minor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salix spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Populus nigra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otros arboles ripicolas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eucalyptus globulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eucalyptus camaldulensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otros eucaliptos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eucalyptus nitens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ilex aquifolium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olea europaea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceratonia siliqua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbutus unedo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fagus sylvatica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Castanea sativa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betula spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corylus avellana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juglans regia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acer campestre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tilia spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbus spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platanus hispanica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myrica faya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ilex canariensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erica arborea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Persea indica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sideroxylon marmulano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Picconia excelsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocotea foetens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apollonias barbujana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otras laurisilvas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robinia pseudoacacia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laurus nobilis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prunus spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhus coriaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sambucus nigra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carpinus betulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otras frondosas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acacia melanoxylon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crataegus monogyna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cedrus deodara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tetraclinis articulata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larix decidua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cupressus arizonica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juniperus oxycedrus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juniperus turbinata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quercus pubescens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quercus lusitanica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quercus ilex ssp. ilex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamarix canariensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraxinus excelsior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulmus glabra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salix alba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Populus x canadensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eucalyptus viminalis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbutus canariensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betula alba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juglans nigra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acer monspessulanum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tilia cordata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbus aria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platanus orientalis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myrica rivas-martinezii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ilex platyphylla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erica scoparia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pleiomeris canariensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sophora japonica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pistacia atlantica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laurus azorica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ficus carica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acacia dealbata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crataegus laevigata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cedrus libani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thuja spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larix leptolepis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cupressus lusitanica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juniperus cedrus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quercus alpestris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraxinus ornus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulmus pumila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salix atrocinerea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eucalyptus gomphocephalus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betula pendula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acer negundo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tilia platyphyllos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbus aucuparia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhamnus glandulosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gleditsia triacanthos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prunus avium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morus spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crataegus laciniata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larix x eurolepis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cupressus macrocarpa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraxinus spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulmus spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salix babylonica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eucalyptus robusta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix canariensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acer opalus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbus domestica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visnea mocanera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prunus lusitanica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morus alba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crataegus azarolus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salix cantabrica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dracaena draco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acer pseudoplatanus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbus torminalis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prunus padus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morus nigra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salix caprea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acer platanoides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbus latifolia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salix elaeagnos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acer spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbus chamaemespilus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salix fragilis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salix canariensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salix purpurea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código provincia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre provincia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Albacete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alicante/Alacant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Almería</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Araba/Álava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asturias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ávila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Badajoz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balears, Illes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barcelona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bizkaia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burgos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cáceres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cádiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantabria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Castellón/Castelló</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceuta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciudad Real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Córdoba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coruña, A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuenca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gipuzkoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Girona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guadalajara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huelva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huesca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">León</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lleida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lugo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Málaga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navarra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ourense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palmas, Las</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pontevedra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rioja, La</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salamanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Cruz de Tenerife</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segovia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sevilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarragona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teruel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toledo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valencia/València</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valladolid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zamora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zaragoza</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="0"/>
+    <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -115,21 +875,22 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <u val="single"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,8 +905,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8CB"/>
-        <bgColor rgb="FFFFDBB6"/>
+        <fgColor rgb="FFFFDBB6"/>
+        <bgColor rgb="FFFFD7D7"/>
       </patternFill>
     </fill>
     <fill>
@@ -156,20 +917,44 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00A933"/>
-        <bgColor rgb="FF008000"/>
+        <fgColor rgb="FFFF8000"/>
+        <bgColor rgb="FFFF6600"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFDBB6"/>
+        <fgColor rgb="FFD1D1D1"/>
         <bgColor rgb="FFFFD7D7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF8000"/>
-        <bgColor rgb="FFFF6600"/>
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81D41A"/>
+        <bgColor rgb="FFD4EA6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EA6B"/>
+        <bgColor rgb="FFFFDBB6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF003300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9D4"/>
+        <bgColor rgb="FFFFFFD7"/>
       </patternFill>
     </fill>
   </fills>
@@ -207,49 +992,113 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -277,16 +1126,16 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFFFD7D7"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFD7D7"/>
+      <rgbColor rgb="FFFFFFD7"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF2A6099"/>
+      <rgbColor rgb="FFD1D1D1"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -297,22 +1146,22 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFDDE8CB"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFD4EA6B"/>
+      <rgbColor rgb="FFF6F9D4"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFDBB6"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FF81D41A"/>
+      <rgbColor rgb="FFFFC000"/>
       <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF00A933"/>
+      <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -324,39 +1173,156 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFFF0000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="20.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="22.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="12.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="991" min="990" style="0" width="11.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1015" min="992" style="0" width="9.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1016" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="9.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="20.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="23.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="13.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="992" min="991" style="4" width="11.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1016" min="993" style="4" width="9.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1017" style="4" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -366,14 +1332,14 @@
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -383,14 +1349,17 @@
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
+      <c r="C3" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -400,14 +1369,14 @@
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -417,14 +1386,17 @@
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -434,16 +1406,19 @@
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="W6" s="6"/>
+      <c r="X6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -452,14 +1427,17 @@
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>11</v>
+      <c r="C7" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -469,14 +1447,17 @@
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>7</v>
+      <c r="C8" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -486,14 +1467,14 @@
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>7</v>
+      <c r="D9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -508,8 +1489,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFFFFFD7"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G100"/>
@@ -519,35 +1501,35 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.18"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="16.29"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="966" min="949" style="0" width="11.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1022" min="967" style="0" width="9.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1023" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="10" width="16.29"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="10" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="966" min="949" style="4" width="11.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1022" min="967" style="4" width="9.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1023" style="4" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="9" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="D1" s="5" t="s">
         <v>17</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -563,10 +1545,10 @@
       <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="7" t="n">
+      <c r="E2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="10" t="n">
         <v>20</v>
       </c>
     </row>
@@ -583,10 +1565,10 @@
       <c r="D3" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="E3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7" t="n">
+      <c r="E3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10" t="n">
         <v>20</v>
       </c>
     </row>
@@ -603,10 +1585,10 @@
       <c r="D4" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="E4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="7" t="n">
+      <c r="E4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10" t="n">
         <v>20</v>
       </c>
     </row>
@@ -623,10 +1605,10 @@
       <c r="D5" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="E5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="7" t="n">
+      <c r="E5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10" t="n">
         <v>20</v>
       </c>
     </row>
@@ -643,10 +1625,10 @@
       <c r="D6" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="E6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="7" t="n">
+      <c r="E6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -663,10 +1645,10 @@
       <c r="D7" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="E7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="7" t="n">
+      <c r="E7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -683,10 +1665,10 @@
       <c r="D8" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="7" t="n">
+      <c r="E8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -703,10 +1685,10 @@
       <c r="D9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="7" t="n">
+      <c r="E9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -723,10 +1705,10 @@
       <c r="D10" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="7" t="n">
+      <c r="E10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -743,10 +1725,10 @@
       <c r="D11" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="E11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="7" t="n">
+      <c r="E11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -763,10 +1745,10 @@
       <c r="D12" s="1" t="n">
         <v>307</v>
       </c>
-      <c r="E12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="7" t="n">
+      <c r="E12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -783,10 +1765,10 @@
       <c r="D13" s="1" t="n">
         <v>207</v>
       </c>
-      <c r="E13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="7" t="n">
+      <c r="E13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -803,10 +1785,10 @@
       <c r="D14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="E14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="7" t="n">
+      <c r="E14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -823,10 +1805,10 @@
       <c r="D15" s="1" t="n">
         <v>76</v>
       </c>
-      <c r="E15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="7" t="n">
+      <c r="E15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -843,10 +1825,10 @@
       <c r="D16" s="1" t="n">
         <v>276</v>
       </c>
-      <c r="E16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="7" t="n">
+      <c r="E16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -863,10 +1845,10 @@
       <c r="D17" s="1" t="n">
         <v>476</v>
       </c>
-      <c r="E17" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="7" t="n">
+      <c r="E17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -883,10 +1865,10 @@
       <c r="D18" s="1" t="n">
         <v>576</v>
       </c>
-      <c r="E18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="7" t="n">
+      <c r="E18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -903,10 +1885,10 @@
       <c r="D19" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="E19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="7" t="n">
+      <c r="E19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -923,10 +1905,10 @@
       <c r="D20" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="E20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="7" t="n">
+      <c r="E20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -943,10 +1925,10 @@
       <c r="D21" s="1" t="n">
         <v>273</v>
       </c>
-      <c r="E21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="7" t="n">
+      <c r="E21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -963,10 +1945,10 @@
       <c r="D22" s="1" t="n">
         <v>373</v>
       </c>
-      <c r="E22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="7" t="n">
+      <c r="E22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -983,10 +1965,10 @@
       <c r="D23" s="1" t="n">
         <v>73</v>
       </c>
-      <c r="E23" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="7" t="n">
+      <c r="E23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1003,10 +1985,10 @@
       <c r="D24" s="1" t="n">
         <v>72</v>
       </c>
-      <c r="E24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="7" t="n">
+      <c r="E24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1023,10 +2005,10 @@
       <c r="D25" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="E25" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="7" t="n">
+      <c r="E25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1043,10 +2025,10 @@
       <c r="D26" s="1" t="n">
         <v>317</v>
       </c>
-      <c r="E26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="7" t="n">
+      <c r="E26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1063,10 +2045,10 @@
       <c r="D27" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E27" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="7" t="n">
+      <c r="E27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1083,10 +2065,10 @@
       <c r="D28" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="E28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="7" t="n">
+      <c r="E28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1103,10 +2085,10 @@
       <c r="D29" s="1" t="n">
         <v>74</v>
       </c>
-      <c r="E29" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="7" t="n">
+      <c r="E29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1123,10 +2105,10 @@
       <c r="D30" s="1" t="n">
         <v>215</v>
       </c>
-      <c r="E30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="7" t="n">
+      <c r="E30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1143,10 +2125,10 @@
       <c r="D31" s="1" t="n">
         <v>236</v>
       </c>
-      <c r="E31" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="7" t="n">
+      <c r="E31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1163,10 +2145,10 @@
       <c r="D32" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="E32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="7" t="n">
+      <c r="E32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1183,10 +2165,10 @@
       <c r="D33" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="E33" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="7" t="n">
+      <c r="E33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1203,10 +2185,10 @@
       <c r="D34" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="E34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="7" t="n">
+      <c r="E34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1223,10 +2205,10 @@
       <c r="D35" s="1" t="n">
         <v>364</v>
       </c>
-      <c r="E35" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="7" t="n">
+      <c r="E35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1243,10 +2225,10 @@
       <c r="D36" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="E36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="7" t="n">
+      <c r="E36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1263,10 +2245,10 @@
       <c r="D37" s="1" t="n">
         <v>464</v>
       </c>
-      <c r="E37" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="7" t="n">
+      <c r="E37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1283,10 +2265,10 @@
       <c r="D38" s="1" t="n">
         <v>264</v>
       </c>
-      <c r="E38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="7" t="n">
+      <c r="E38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1303,10 +2285,10 @@
       <c r="D39" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="E39" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="7" t="n">
+      <c r="E39" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1323,10 +2305,10 @@
       <c r="D40" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="E40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="7" t="n">
+      <c r="E40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1343,10 +2325,10 @@
       <c r="D41" s="1" t="n">
         <v>255</v>
       </c>
-      <c r="E41" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="7" t="n">
+      <c r="E41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1363,10 +2345,10 @@
       <c r="D42" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="E42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="7" t="n">
+      <c r="E42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1383,10 +2365,10 @@
       <c r="D43" s="1" t="n">
         <v>82</v>
       </c>
-      <c r="E43" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="7" t="n">
+      <c r="E43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1403,10 +2385,10 @@
       <c r="D44" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="E44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="7" t="n">
+      <c r="E44" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1423,10 +2405,10 @@
       <c r="D45" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="E45" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="7" t="n">
+      <c r="E45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1443,10 +2425,10 @@
       <c r="D46" s="1" t="n">
         <v>237</v>
       </c>
-      <c r="E46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="7" t="n">
+      <c r="E46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1463,10 +2445,10 @@
       <c r="D47" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="E47" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="7" t="n">
+      <c r="E47" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1483,10 +2465,10 @@
       <c r="D48" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="E48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="7" t="n">
+      <c r="E48" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1503,10 +2485,10 @@
       <c r="D49" s="1" t="n">
         <v>235</v>
       </c>
-      <c r="E49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="7" t="n">
+      <c r="E49" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1523,10 +2505,10 @@
       <c r="D50" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="E50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="7" t="n">
+      <c r="E50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1543,10 +2525,10 @@
       <c r="D51" s="1" t="n">
         <v>294</v>
       </c>
-      <c r="E51" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="7" t="n">
+      <c r="E51" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1563,10 +2545,10 @@
       <c r="D52" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="E52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="7" t="n">
+      <c r="E52" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1583,10 +2565,10 @@
       <c r="D53" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="E53" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="7" t="n">
+      <c r="E53" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1603,10 +2585,10 @@
       <c r="D54" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="E54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="7" t="n">
+      <c r="E54" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1623,10 +2605,10 @@
       <c r="D55" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="E55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="7" t="n">
+      <c r="E55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1643,10 +2625,10 @@
       <c r="D56" s="1" t="n">
         <v>84</v>
       </c>
-      <c r="E56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="7" t="n">
+      <c r="E56" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1663,10 +2645,10 @@
       <c r="D57" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E57" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="7" t="n">
+      <c r="E57" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1683,10 +2665,10 @@
       <c r="D58" s="1" t="n">
         <v>469</v>
       </c>
-      <c r="E58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="7" t="n">
+      <c r="E58" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1703,10 +2685,10 @@
       <c r="D59" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="E59" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="7" t="n">
+      <c r="E59" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1723,10 +2705,10 @@
       <c r="D60" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="E60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="7" t="n">
+      <c r="E60" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1743,10 +2725,10 @@
       <c r="D61" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="E61" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="7" t="n">
+      <c r="E61" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1763,10 +2745,10 @@
       <c r="D62" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="E62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="7" t="n">
+      <c r="E62" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1783,10 +2765,10 @@
       <c r="D63" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="E63" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="7" t="n">
+      <c r="E63" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1803,10 +2785,10 @@
       <c r="D64" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="E64" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="7" t="n">
+      <c r="E64" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1823,10 +2805,10 @@
       <c r="D65" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="E65" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="7" t="n">
+      <c r="E65" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1843,10 +2825,10 @@
       <c r="D66" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="E66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="7" t="n">
+      <c r="E66" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1863,10 +2845,10 @@
       <c r="D67" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="E67" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="7" t="n">
+      <c r="E67" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1883,10 +2865,10 @@
       <c r="D68" s="1" t="n">
         <v>79</v>
       </c>
-      <c r="E68" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" s="7" t="n">
+      <c r="E68" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1903,10 +2885,10 @@
       <c r="D69" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="E69" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="7" t="n">
+      <c r="E69" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1923,10 +2905,10 @@
       <c r="D70" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="E70" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="7" t="n">
+      <c r="E70" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1943,10 +2925,10 @@
       <c r="D71" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="E71" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="7" t="n">
+      <c r="E71" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1963,10 +2945,10 @@
       <c r="D72" s="1" t="n">
         <v>258</v>
       </c>
-      <c r="E72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="7" t="n">
+      <c r="E72" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1983,10 +2965,10 @@
       <c r="D73" s="1" t="n">
         <v>395</v>
       </c>
-      <c r="E73" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="7" t="n">
+      <c r="E73" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2003,10 +2985,10 @@
       <c r="D74" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="E74" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="7" t="n">
+      <c r="E74" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2023,10 +3005,10 @@
       <c r="D75" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="E75" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="7" t="n">
+      <c r="E75" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2043,10 +3025,10 @@
       <c r="D76" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="E76" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="7" t="n">
+      <c r="E76" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2063,10 +3045,10 @@
       <c r="D77" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="E77" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="7" t="n">
+      <c r="E77" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2083,10 +3065,10 @@
       <c r="D78" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="E78" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="7" t="n">
+      <c r="E78" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2103,10 +3085,10 @@
       <c r="D79" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="E79" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="7" t="n">
+      <c r="E79" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2123,10 +3105,10 @@
       <c r="D80" s="1" t="n">
         <v>243</v>
       </c>
-      <c r="E80" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="7" t="n">
+      <c r="E80" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2143,10 +3125,10 @@
       <c r="D81" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="E81" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="7" t="n">
+      <c r="E81" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2163,10 +3145,10 @@
       <c r="D82" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="E82" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" s="7" t="n">
+      <c r="E82" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2183,10 +3165,10 @@
       <c r="D83" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="E83" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="7" t="n">
+      <c r="E83" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2203,10 +3185,10 @@
       <c r="D84" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="E84" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="7" t="n">
+      <c r="E84" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2223,10 +3205,10 @@
       <c r="D85" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="E85" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" s="7" t="n">
+      <c r="E85" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2243,10 +3225,10 @@
       <c r="D86" s="1" t="n">
         <v>257</v>
       </c>
-      <c r="E86" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" s="7" t="n">
+      <c r="E86" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2263,10 +3245,10 @@
       <c r="D87" s="1" t="n">
         <v>357</v>
       </c>
-      <c r="E87" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" s="7" t="n">
+      <c r="E87" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2283,10 +3265,10 @@
       <c r="D88" s="1" t="n">
         <v>657</v>
       </c>
-      <c r="E88" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="7" t="n">
+      <c r="E88" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2303,10 +3285,10 @@
       <c r="D89" s="1" t="n">
         <v>857</v>
       </c>
-      <c r="E89" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" s="7" t="n">
+      <c r="E89" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2323,10 +3305,10 @@
       <c r="D90" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="E90" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" s="7" t="n">
+      <c r="E90" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2343,10 +3325,10 @@
       <c r="D91" s="1" t="n">
         <v>278</v>
       </c>
-      <c r="E91" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" s="7" t="n">
+      <c r="E91" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2363,10 +3345,10 @@
       <c r="D92" s="1" t="n">
         <v>378</v>
       </c>
-      <c r="E92" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="7" t="n">
+      <c r="E92" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2383,10 +3365,10 @@
       <c r="D93" s="1" t="n">
         <v>78</v>
       </c>
-      <c r="E93" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" s="7" t="n">
+      <c r="E93" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2403,10 +3385,10 @@
       <c r="D94" s="1" t="n">
         <v>578</v>
       </c>
-      <c r="E94" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F94" s="7" t="n">
+      <c r="E94" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2423,10 +3405,10 @@
       <c r="D95" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E95" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" s="7" t="n">
+      <c r="E95" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2443,10 +3425,10 @@
       <c r="D96" s="1" t="n">
         <v>277</v>
       </c>
-      <c r="E96" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="7" t="n">
+      <c r="E96" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2463,10 +3445,10 @@
       <c r="D97" s="1" t="n">
         <v>377</v>
       </c>
-      <c r="E97" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" s="7" t="n">
+      <c r="E97" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2483,10 +3465,10 @@
       <c r="D98" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="E98" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="7" t="n">
+      <c r="E98" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2503,10 +3485,10 @@
       <c r="D99" s="1" t="n">
         <v>256</v>
       </c>
-      <c r="E99" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" s="7" t="n">
+      <c r="E99" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2523,10 +3505,10 @@
       <c r="D100" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="E100" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="7" t="n">
+      <c r="E100" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2539,4 +3521,4994 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF2A6099"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="21.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="63.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="23.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="21.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="159.66"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="D6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="D7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="D8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="D9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D12" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D13" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D17" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D18" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D21" s="8"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D25" s="8"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D26" s="8"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D30" s="8"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D31" s="8"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D32" s="8"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D33" s="8"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D34" s="8"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D36" s="8"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D37" s="8"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D38" s="8"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D39" s="8"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D40" s="8"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D41" s="8"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D42" s="8"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D43" s="8"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D44" s="8"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D45" s="8"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D46" s="8"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D47" s="8"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D48" s="8"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D49" s="8"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D50" s="8"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D51" s="8"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D52" s="8"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D53" s="8"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D54" s="8"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D55" s="8"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D56" s="8"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D57" s="8"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D58" s="8"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D59" s="8"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D60" s="8"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D61" s="8"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D62" s="8"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D63" s="8"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D64" s="8"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D65" s="8"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D66" s="8"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D67" s="8"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D68" s="8"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D69" s="8"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D70" s="8"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D71" s="8"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D72" s="8"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D73" s="8"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D74" s="8"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D75" s="8"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D76" s="8"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D77" s="8"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D78" s="8"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D79" s="8"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D80" s="8"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D81" s="8"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D82" s="8"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D83" s="8"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D84" s="8"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D85" s="8"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D86" s="8"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D87" s="8"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D88" s="8"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D89" s="8"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D90" s="8"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D91" s="8"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D92" s="8"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D93" s="8"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D94" s="8"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D95" s="8"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D96" s="8"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D97" s="8"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D98" s="8"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D99" s="8"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D100" s="8"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D101" s="8"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D102" s="8"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D103" s="8"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D104" s="8"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D105" s="8"/>
+    </row>
+    <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D106" s="8"/>
+    </row>
+    <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D107" s="8"/>
+    </row>
+    <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D108" s="8"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D109" s="8"/>
+    </row>
+    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D110" s="8"/>
+    </row>
+    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D111" s="8"/>
+    </row>
+    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D112" s="8"/>
+    </row>
+    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D113" s="8"/>
+    </row>
+    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D114" s="8"/>
+    </row>
+    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D115" s="8"/>
+    </row>
+    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D116" s="8"/>
+    </row>
+    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D117" s="8"/>
+    </row>
+    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D118" s="8"/>
+    </row>
+    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D119" s="8"/>
+    </row>
+    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D120" s="8"/>
+    </row>
+    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D121" s="8"/>
+    </row>
+    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D122" s="8"/>
+    </row>
+    <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D123" s="8"/>
+    </row>
+    <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D124" s="8"/>
+    </row>
+    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D125" s="8"/>
+    </row>
+    <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D126" s="8"/>
+    </row>
+    <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D127" s="8"/>
+    </row>
+    <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D128" s="8"/>
+    </row>
+    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D129" s="8"/>
+    </row>
+    <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D130" s="8"/>
+    </row>
+    <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D131" s="8"/>
+    </row>
+    <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D132" s="8"/>
+    </row>
+    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D133" s="8"/>
+    </row>
+    <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D134" s="8"/>
+    </row>
+    <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D135" s="8"/>
+    </row>
+    <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D136" s="8"/>
+    </row>
+    <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D137" s="8"/>
+    </row>
+    <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D138" s="8"/>
+    </row>
+    <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D139" s="8"/>
+    </row>
+    <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D140" s="8"/>
+    </row>
+    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D141" s="8"/>
+    </row>
+    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D142" s="8"/>
+    </row>
+    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D143" s="8"/>
+    </row>
+    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D144" s="8"/>
+    </row>
+    <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D145" s="8"/>
+    </row>
+    <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D146" s="8"/>
+    </row>
+    <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D147" s="8"/>
+    </row>
+    <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D148" s="8"/>
+    </row>
+    <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D149" s="8"/>
+    </row>
+    <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D150" s="8"/>
+    </row>
+    <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D151" s="8"/>
+    </row>
+    <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D152" s="8"/>
+    </row>
+    <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D153" s="8"/>
+    </row>
+    <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D154" s="8"/>
+    </row>
+    <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D155" s="8"/>
+    </row>
+    <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D156" s="8"/>
+    </row>
+    <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D157" s="8"/>
+    </row>
+    <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D158" s="8"/>
+    </row>
+    <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D159" s="8"/>
+    </row>
+    <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D160" s="8"/>
+    </row>
+    <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D161" s="8"/>
+    </row>
+    <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D162" s="8"/>
+    </row>
+    <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D163" s="8"/>
+    </row>
+    <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D164" s="8"/>
+    </row>
+    <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D165" s="8"/>
+    </row>
+    <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D166" s="8"/>
+    </row>
+    <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D167" s="8"/>
+    </row>
+    <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D168" s="8"/>
+    </row>
+    <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D169" s="8"/>
+    </row>
+    <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D170" s="8"/>
+    </row>
+    <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D171" s="8"/>
+    </row>
+    <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D172" s="8"/>
+    </row>
+    <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D173" s="8"/>
+    </row>
+    <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D174" s="8"/>
+    </row>
+    <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D175" s="8"/>
+    </row>
+    <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D176" s="8"/>
+    </row>
+    <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D177" s="8"/>
+    </row>
+    <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D178" s="8"/>
+    </row>
+    <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D179" s="8"/>
+    </row>
+    <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D180" s="8"/>
+    </row>
+    <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D181" s="8"/>
+    </row>
+    <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D182" s="8"/>
+    </row>
+    <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D183" s="8"/>
+    </row>
+    <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D184" s="8"/>
+    </row>
+    <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D185" s="8"/>
+    </row>
+    <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D186" s="8"/>
+    </row>
+    <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D187" s="8"/>
+    </row>
+    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D188" s="8"/>
+    </row>
+    <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D189" s="8"/>
+    </row>
+    <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D190" s="8"/>
+    </row>
+    <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D191" s="8"/>
+    </row>
+    <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D192" s="8"/>
+    </row>
+    <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D193" s="8"/>
+    </row>
+    <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D194" s="8"/>
+    </row>
+    <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D195" s="8"/>
+    </row>
+    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D196" s="8"/>
+    </row>
+    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D197" s="8"/>
+    </row>
+    <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D198" s="8"/>
+    </row>
+    <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D199" s="8"/>
+    </row>
+    <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D200" s="8"/>
+    </row>
+    <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D201" s="8"/>
+    </row>
+    <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D202" s="8"/>
+    </row>
+    <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D203" s="8"/>
+    </row>
+    <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D204" s="8"/>
+    </row>
+    <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D205" s="8"/>
+    </row>
+    <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D206" s="8"/>
+    </row>
+    <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D207" s="8"/>
+    </row>
+    <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D208" s="8"/>
+    </row>
+    <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D209" s="8"/>
+    </row>
+    <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D210" s="8"/>
+    </row>
+    <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D211" s="8"/>
+    </row>
+    <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D212" s="8"/>
+    </row>
+    <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D213" s="8"/>
+    </row>
+    <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D214" s="8"/>
+    </row>
+    <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D215" s="8"/>
+    </row>
+    <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D216" s="8"/>
+    </row>
+    <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D217" s="8"/>
+    </row>
+    <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D218" s="8"/>
+    </row>
+    <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D219" s="8"/>
+    </row>
+    <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D220" s="8"/>
+    </row>
+    <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D221" s="8"/>
+    </row>
+    <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D222" s="8"/>
+    </row>
+    <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D223" s="8"/>
+    </row>
+    <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D224" s="8"/>
+    </row>
+    <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D225" s="8"/>
+    </row>
+    <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D226" s="8"/>
+    </row>
+    <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D227" s="8"/>
+    </row>
+    <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D228" s="8"/>
+    </row>
+    <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D229" s="8"/>
+    </row>
+    <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D230" s="8"/>
+    </row>
+    <row r="231" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D231" s="8"/>
+    </row>
+    <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D232" s="8"/>
+    </row>
+    <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D233" s="8"/>
+    </row>
+    <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D234" s="8"/>
+    </row>
+    <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D235" s="8"/>
+    </row>
+    <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D236" s="8"/>
+    </row>
+    <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D237" s="8"/>
+    </row>
+    <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D238" s="8"/>
+    </row>
+    <row r="239" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D239" s="8"/>
+    </row>
+    <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D240" s="8"/>
+    </row>
+    <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D241" s="8"/>
+    </row>
+    <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D242" s="8"/>
+    </row>
+    <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D243" s="8"/>
+    </row>
+    <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D244" s="8"/>
+    </row>
+    <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D245" s="8"/>
+    </row>
+    <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D246" s="8"/>
+    </row>
+    <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D247" s="8"/>
+    </row>
+    <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D248" s="8"/>
+    </row>
+    <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D249" s="8"/>
+    </row>
+    <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D250" s="8"/>
+    </row>
+    <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D251" s="8"/>
+    </row>
+    <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D252" s="8"/>
+    </row>
+    <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D253" s="8"/>
+    </row>
+    <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D254" s="8"/>
+    </row>
+    <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D255" s="8"/>
+    </row>
+    <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D256" s="8"/>
+    </row>
+    <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D257" s="8"/>
+    </row>
+    <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D258" s="8"/>
+    </row>
+    <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D259" s="8"/>
+    </row>
+    <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D260" s="8"/>
+    </row>
+    <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D261" s="8"/>
+    </row>
+    <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D262" s="8"/>
+    </row>
+    <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D263" s="8"/>
+    </row>
+    <row r="264" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D264" s="8"/>
+    </row>
+    <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D265" s="8"/>
+    </row>
+    <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D266" s="8"/>
+    </row>
+    <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D267" s="8"/>
+    </row>
+    <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D268" s="8"/>
+    </row>
+    <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D269" s="8"/>
+    </row>
+    <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D270" s="8"/>
+    </row>
+    <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D271" s="8"/>
+    </row>
+    <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D272" s="8"/>
+    </row>
+    <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D273" s="8"/>
+    </row>
+    <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D274" s="8"/>
+    </row>
+    <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D275" s="8"/>
+    </row>
+    <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D276" s="8"/>
+    </row>
+    <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D277" s="8"/>
+    </row>
+    <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D278" s="8"/>
+    </row>
+    <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D279" s="8"/>
+    </row>
+    <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D280" s="8"/>
+    </row>
+    <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D281" s="8"/>
+    </row>
+    <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D282" s="8"/>
+    </row>
+    <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D283" s="8"/>
+    </row>
+    <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D284" s="8"/>
+    </row>
+    <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D285" s="8"/>
+    </row>
+    <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D286" s="8"/>
+    </row>
+    <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D287" s="8"/>
+    </row>
+    <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D288" s="8"/>
+    </row>
+    <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D289" s="8"/>
+    </row>
+    <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D290" s="8"/>
+    </row>
+    <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D291" s="8"/>
+    </row>
+    <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D292" s="8"/>
+    </row>
+    <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D293" s="8"/>
+    </row>
+    <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D294" s="8"/>
+    </row>
+    <row r="295" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D295" s="8"/>
+    </row>
+    <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D296" s="8"/>
+    </row>
+    <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D297" s="8"/>
+    </row>
+    <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D298" s="8"/>
+    </row>
+    <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D299" s="8"/>
+    </row>
+    <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D300" s="8"/>
+    </row>
+    <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D301" s="8"/>
+    </row>
+    <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D302" s="8"/>
+    </row>
+    <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D303" s="8"/>
+    </row>
+    <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D304" s="8"/>
+    </row>
+    <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D305" s="8"/>
+    </row>
+    <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D306" s="8"/>
+    </row>
+    <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D307" s="8"/>
+    </row>
+    <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D308" s="8"/>
+    </row>
+    <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D309" s="8"/>
+    </row>
+    <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D310" s="8"/>
+    </row>
+    <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D311" s="8"/>
+    </row>
+    <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D312" s="8"/>
+    </row>
+    <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D313" s="8"/>
+    </row>
+    <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D314" s="8"/>
+    </row>
+    <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D315" s="8"/>
+    </row>
+    <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D316" s="8"/>
+    </row>
+    <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D317" s="8"/>
+    </row>
+    <row r="318" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D318" s="8"/>
+    </row>
+    <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D319" s="8"/>
+    </row>
+    <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D320" s="8"/>
+    </row>
+    <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D321" s="8"/>
+    </row>
+    <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D322" s="8"/>
+    </row>
+    <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D323" s="8"/>
+    </row>
+    <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D324" s="8"/>
+    </row>
+    <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D325" s="8"/>
+    </row>
+    <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D326" s="8"/>
+    </row>
+    <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D327" s="8"/>
+    </row>
+    <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D328" s="8"/>
+    </row>
+    <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D329" s="8"/>
+    </row>
+    <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D330" s="8"/>
+    </row>
+    <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D331" s="8"/>
+    </row>
+    <row r="332" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D332" s="8"/>
+    </row>
+    <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D333" s="8"/>
+    </row>
+    <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D334" s="8"/>
+    </row>
+    <row r="335" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D335" s="8"/>
+    </row>
+    <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D336" s="8"/>
+    </row>
+    <row r="337" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D337" s="8"/>
+    </row>
+    <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D338" s="8"/>
+    </row>
+    <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D339" s="8"/>
+    </row>
+    <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D340" s="8"/>
+    </row>
+    <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D341" s="8"/>
+    </row>
+    <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D342" s="8"/>
+    </row>
+    <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D343" s="8"/>
+    </row>
+    <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D344" s="8"/>
+    </row>
+    <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D345" s="8"/>
+    </row>
+    <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D346" s="8"/>
+    </row>
+    <row r="347" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D347" s="8"/>
+    </row>
+    <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D348" s="8"/>
+    </row>
+    <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D349" s="8"/>
+    </row>
+    <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D350" s="8"/>
+    </row>
+    <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D351" s="8"/>
+    </row>
+    <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D352" s="8"/>
+    </row>
+    <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D353" s="8"/>
+    </row>
+    <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D354" s="8"/>
+    </row>
+    <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D355" s="8"/>
+    </row>
+    <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D356" s="8"/>
+    </row>
+    <row r="357" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D357" s="8"/>
+    </row>
+    <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D358" s="8"/>
+    </row>
+    <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D359" s="8"/>
+    </row>
+    <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D360" s="8"/>
+    </row>
+    <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D361" s="8"/>
+    </row>
+    <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D362" s="8"/>
+    </row>
+    <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D363" s="8"/>
+    </row>
+    <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D364" s="8"/>
+    </row>
+    <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D365" s="8"/>
+    </row>
+    <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D366" s="8"/>
+    </row>
+    <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D367" s="8"/>
+    </row>
+    <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D368" s="8"/>
+    </row>
+    <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D369" s="8"/>
+    </row>
+    <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D370" s="8"/>
+    </row>
+    <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D371" s="8"/>
+    </row>
+    <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D372" s="8"/>
+    </row>
+    <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D373" s="8"/>
+    </row>
+    <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D374" s="8"/>
+    </row>
+    <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D375" s="8"/>
+    </row>
+    <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D376" s="8"/>
+    </row>
+    <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D377" s="8"/>
+    </row>
+    <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D378" s="8"/>
+    </row>
+    <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D379" s="8"/>
+    </row>
+    <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D380" s="8"/>
+    </row>
+    <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D381" s="8"/>
+    </row>
+    <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D382" s="8"/>
+    </row>
+    <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D383" s="8"/>
+    </row>
+    <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D384" s="8"/>
+    </row>
+    <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D385" s="8"/>
+    </row>
+    <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D386" s="8"/>
+    </row>
+    <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D387" s="8"/>
+    </row>
+    <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D388" s="8"/>
+    </row>
+    <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D389" s="8"/>
+    </row>
+    <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D390" s="8"/>
+    </row>
+    <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D391" s="8"/>
+    </row>
+    <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D392" s="8"/>
+    </row>
+    <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D393" s="8"/>
+    </row>
+    <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D394" s="8"/>
+    </row>
+    <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D395" s="8"/>
+    </row>
+    <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D396" s="8"/>
+    </row>
+    <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D397" s="8"/>
+    </row>
+    <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D398" s="8"/>
+    </row>
+    <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D399" s="8"/>
+    </row>
+    <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D400" s="8"/>
+    </row>
+    <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D401" s="8"/>
+    </row>
+    <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D402" s="8"/>
+    </row>
+    <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D403" s="8"/>
+    </row>
+    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D404" s="8"/>
+    </row>
+    <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D405" s="8"/>
+    </row>
+    <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D406" s="8"/>
+    </row>
+    <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D407" s="8"/>
+    </row>
+    <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D408" s="8"/>
+    </row>
+    <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D409" s="8"/>
+    </row>
+    <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D410" s="8"/>
+    </row>
+    <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D411" s="8"/>
+    </row>
+    <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D412" s="8"/>
+    </row>
+    <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D413" s="8"/>
+    </row>
+    <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D414" s="8"/>
+    </row>
+    <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D415" s="8"/>
+    </row>
+    <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D416" s="8"/>
+    </row>
+    <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D417" s="8"/>
+    </row>
+    <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D418" s="8"/>
+    </row>
+    <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D419" s="8"/>
+    </row>
+    <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D420" s="8"/>
+    </row>
+    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D421" s="8"/>
+    </row>
+    <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D422" s="8"/>
+    </row>
+    <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D423" s="8"/>
+    </row>
+    <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D424" s="8"/>
+    </row>
+    <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D425" s="8"/>
+    </row>
+    <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D426" s="8"/>
+    </row>
+    <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D427" s="8"/>
+    </row>
+    <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D428" s="8"/>
+    </row>
+    <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D429" s="8"/>
+    </row>
+    <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D430" s="8"/>
+    </row>
+    <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D431" s="8"/>
+    </row>
+    <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D432" s="8"/>
+    </row>
+    <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D433" s="8"/>
+    </row>
+    <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D434" s="8"/>
+    </row>
+    <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D435" s="8"/>
+    </row>
+    <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D436" s="8"/>
+    </row>
+    <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D437" s="8"/>
+    </row>
+    <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D438" s="8"/>
+    </row>
+    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D439" s="8"/>
+    </row>
+    <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D440" s="8"/>
+    </row>
+    <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D441" s="8"/>
+    </row>
+    <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D442" s="8"/>
+    </row>
+    <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D443" s="8"/>
+    </row>
+    <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D444" s="8"/>
+    </row>
+    <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D445" s="8"/>
+    </row>
+    <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D446" s="8"/>
+    </row>
+    <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D447" s="8"/>
+    </row>
+    <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D448" s="8"/>
+    </row>
+    <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D449" s="8"/>
+    </row>
+    <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D450" s="8"/>
+    </row>
+    <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D451" s="8"/>
+    </row>
+    <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D452" s="8"/>
+    </row>
+    <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D453" s="8"/>
+    </row>
+    <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D454" s="8"/>
+    </row>
+    <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D455" s="8"/>
+    </row>
+    <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D456" s="8"/>
+    </row>
+    <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D457" s="8"/>
+    </row>
+    <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D458" s="8"/>
+    </row>
+    <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D459" s="8"/>
+    </row>
+    <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D460" s="8"/>
+    </row>
+    <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D461" s="8"/>
+    </row>
+    <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D462" s="8"/>
+    </row>
+    <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D463" s="8"/>
+    </row>
+    <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D464" s="8"/>
+    </row>
+    <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D465" s="8"/>
+    </row>
+    <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D466" s="8"/>
+    </row>
+    <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D467" s="8"/>
+    </row>
+    <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D468" s="8"/>
+    </row>
+    <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D469" s="8"/>
+    </row>
+    <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D470" s="8"/>
+    </row>
+    <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D471" s="8"/>
+    </row>
+    <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D472" s="8"/>
+    </row>
+    <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D473" s="8"/>
+    </row>
+    <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D474" s="8"/>
+    </row>
+    <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D475" s="8"/>
+    </row>
+    <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D476" s="8"/>
+    </row>
+    <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D477" s="8"/>
+    </row>
+    <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D478" s="8"/>
+    </row>
+    <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D479" s="8"/>
+    </row>
+    <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D480" s="8"/>
+    </row>
+    <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D481" s="8"/>
+    </row>
+    <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D482" s="8"/>
+    </row>
+    <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D483" s="8"/>
+    </row>
+    <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D484" s="8"/>
+    </row>
+    <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D485" s="8"/>
+    </row>
+    <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D486" s="8"/>
+    </row>
+    <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D487" s="8"/>
+    </row>
+    <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D488" s="8"/>
+    </row>
+    <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D489" s="8"/>
+    </row>
+    <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D490" s="8"/>
+    </row>
+    <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D491" s="8"/>
+    </row>
+    <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D492" s="8"/>
+    </row>
+    <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D493" s="8"/>
+    </row>
+    <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D494" s="8"/>
+    </row>
+    <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D495" s="8"/>
+    </row>
+    <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D496" s="8"/>
+    </row>
+    <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D497" s="8"/>
+    </row>
+    <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D498" s="8"/>
+    </row>
+    <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D499" s="8"/>
+    </row>
+    <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D500" s="8"/>
+    </row>
+    <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D501" s="8"/>
+    </row>
+    <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D502" s="8"/>
+    </row>
+    <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D503" s="8"/>
+    </row>
+    <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D504" s="8"/>
+    </row>
+    <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D505" s="8"/>
+    </row>
+    <row r="506" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D506" s="8"/>
+    </row>
+    <row r="507" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D507" s="8"/>
+    </row>
+    <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D508" s="8"/>
+    </row>
+    <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D509" s="8"/>
+    </row>
+    <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D510" s="8"/>
+    </row>
+    <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D511" s="8"/>
+    </row>
+    <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D512" s="8"/>
+    </row>
+    <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D513" s="8"/>
+    </row>
+    <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D514" s="8"/>
+    </row>
+    <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D515" s="8"/>
+    </row>
+    <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D516" s="8"/>
+    </row>
+    <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D517" s="8"/>
+    </row>
+    <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D518" s="8"/>
+    </row>
+    <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D519" s="8"/>
+    </row>
+    <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D520" s="8"/>
+    </row>
+    <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D521" s="8"/>
+    </row>
+    <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D522" s="8"/>
+    </row>
+    <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D523" s="8"/>
+    </row>
+    <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D524" s="8"/>
+    </row>
+    <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D525" s="8"/>
+    </row>
+    <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D526" s="8"/>
+    </row>
+    <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D527" s="8"/>
+    </row>
+    <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D528" s="8"/>
+    </row>
+    <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D529" s="8"/>
+    </row>
+    <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D530" s="8"/>
+    </row>
+    <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D531" s="8"/>
+    </row>
+    <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D532" s="8"/>
+    </row>
+    <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D533" s="8"/>
+    </row>
+    <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D534" s="8"/>
+    </row>
+    <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D535" s="8"/>
+    </row>
+    <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D536" s="8"/>
+    </row>
+    <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D537" s="8"/>
+    </row>
+    <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D538" s="8"/>
+    </row>
+    <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D539" s="8"/>
+    </row>
+    <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D540" s="8"/>
+    </row>
+    <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D541" s="8"/>
+    </row>
+    <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D542" s="8"/>
+    </row>
+    <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D543" s="8"/>
+    </row>
+    <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D544" s="8"/>
+    </row>
+    <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D545" s="8"/>
+    </row>
+    <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D546" s="8"/>
+    </row>
+    <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D547" s="8"/>
+    </row>
+    <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D548" s="8"/>
+    </row>
+    <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D549" s="8"/>
+    </row>
+    <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D550" s="8"/>
+    </row>
+    <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D551" s="8"/>
+    </row>
+    <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D552" s="8"/>
+    </row>
+    <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D553" s="8"/>
+    </row>
+    <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D554" s="8"/>
+    </row>
+    <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D555" s="8"/>
+    </row>
+    <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D556" s="8"/>
+    </row>
+    <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D557" s="8"/>
+    </row>
+    <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D558" s="8"/>
+    </row>
+    <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D559" s="8"/>
+    </row>
+    <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D560" s="8"/>
+    </row>
+    <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D561" s="8"/>
+    </row>
+    <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D562" s="8"/>
+    </row>
+    <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D563" s="8"/>
+    </row>
+    <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D564" s="8"/>
+    </row>
+    <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D565" s="8"/>
+    </row>
+    <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D566" s="8"/>
+    </row>
+    <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D567" s="8"/>
+    </row>
+    <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D568" s="8"/>
+    </row>
+    <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D569" s="8"/>
+    </row>
+    <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D570" s="8"/>
+    </row>
+    <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D571" s="8"/>
+    </row>
+    <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D572" s="8"/>
+    </row>
+    <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D573" s="8"/>
+    </row>
+    <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D574" s="8"/>
+    </row>
+    <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D575" s="8"/>
+    </row>
+    <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D576" s="8"/>
+    </row>
+    <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D577" s="8"/>
+    </row>
+    <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D578" s="8"/>
+    </row>
+    <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D579" s="8"/>
+    </row>
+    <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D580" s="8"/>
+    </row>
+    <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D581" s="8"/>
+    </row>
+    <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D582" s="8"/>
+    </row>
+    <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D583" s="8"/>
+    </row>
+    <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D584" s="8"/>
+    </row>
+    <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D585" s="8"/>
+    </row>
+    <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D586" s="8"/>
+    </row>
+    <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D587" s="8"/>
+    </row>
+    <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D588" s="8"/>
+    </row>
+    <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D589" s="8"/>
+    </row>
+    <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D590" s="8"/>
+    </row>
+    <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D591" s="8"/>
+    </row>
+    <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D592" s="8"/>
+    </row>
+    <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D593" s="8"/>
+    </row>
+    <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D594" s="8"/>
+    </row>
+    <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D595" s="8"/>
+    </row>
+    <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D596" s="8"/>
+    </row>
+    <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D597" s="8"/>
+    </row>
+    <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D598" s="8"/>
+    </row>
+    <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D599" s="8"/>
+    </row>
+    <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D600" s="8"/>
+    </row>
+    <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D601" s="8"/>
+    </row>
+    <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D602" s="8"/>
+    </row>
+    <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D603" s="8"/>
+    </row>
+    <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D604" s="8"/>
+    </row>
+    <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D605" s="8"/>
+    </row>
+    <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D606" s="8"/>
+    </row>
+    <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D607" s="8"/>
+    </row>
+    <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D608" s="8"/>
+    </row>
+    <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D609" s="8"/>
+    </row>
+    <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D610" s="8"/>
+    </row>
+    <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D611" s="8"/>
+    </row>
+    <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D612" s="8"/>
+    </row>
+    <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D613" s="8"/>
+    </row>
+    <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D614" s="8"/>
+    </row>
+    <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D615" s="8"/>
+    </row>
+    <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D616" s="8"/>
+    </row>
+    <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D617" s="8"/>
+    </row>
+    <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D618" s="8"/>
+    </row>
+    <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D619" s="8"/>
+    </row>
+    <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D620" s="8"/>
+    </row>
+    <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D621" s="8"/>
+    </row>
+    <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D622" s="8"/>
+    </row>
+    <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D623" s="8"/>
+    </row>
+    <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D624" s="8"/>
+    </row>
+    <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D625" s="8"/>
+    </row>
+    <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D626" s="8"/>
+    </row>
+    <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D627" s="8"/>
+    </row>
+    <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D628" s="8"/>
+    </row>
+    <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D629" s="8"/>
+    </row>
+    <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D630" s="8"/>
+    </row>
+    <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D631" s="8"/>
+    </row>
+    <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D632" s="8"/>
+    </row>
+    <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D633" s="8"/>
+    </row>
+    <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D634" s="8"/>
+    </row>
+    <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D635" s="8"/>
+    </row>
+    <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D636" s="8"/>
+    </row>
+    <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D637" s="8"/>
+    </row>
+    <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D638" s="8"/>
+    </row>
+    <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D639" s="8"/>
+    </row>
+    <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D640" s="8"/>
+    </row>
+    <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D641" s="8"/>
+    </row>
+    <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D642" s="8"/>
+    </row>
+    <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D643" s="8"/>
+    </row>
+    <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D644" s="8"/>
+    </row>
+    <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D645" s="8"/>
+    </row>
+    <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D646" s="8"/>
+    </row>
+    <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D647" s="8"/>
+    </row>
+    <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D648" s="8"/>
+    </row>
+    <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D649" s="8"/>
+    </row>
+    <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D650" s="8"/>
+    </row>
+    <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D651" s="8"/>
+    </row>
+    <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D652" s="8"/>
+    </row>
+    <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D653" s="8"/>
+    </row>
+    <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D654" s="8"/>
+    </row>
+    <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D655" s="8"/>
+    </row>
+    <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D656" s="8"/>
+    </row>
+    <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D657" s="8"/>
+    </row>
+    <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D658" s="8"/>
+    </row>
+    <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D659" s="8"/>
+    </row>
+    <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D660" s="8"/>
+    </row>
+    <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D661" s="8"/>
+    </row>
+    <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D662" s="8"/>
+    </row>
+    <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D663" s="8"/>
+    </row>
+    <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D664" s="8"/>
+    </row>
+    <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D665" s="8"/>
+    </row>
+    <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D666" s="8"/>
+    </row>
+    <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D667" s="8"/>
+    </row>
+    <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D668" s="8"/>
+    </row>
+    <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D669" s="8"/>
+    </row>
+    <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D670" s="8"/>
+    </row>
+    <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D671" s="8"/>
+    </row>
+    <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D672" s="8"/>
+    </row>
+    <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D673" s="8"/>
+    </row>
+    <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D674" s="8"/>
+    </row>
+    <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D675" s="8"/>
+    </row>
+    <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D676" s="8"/>
+    </row>
+    <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D677" s="8"/>
+    </row>
+    <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D678" s="8"/>
+    </row>
+    <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D679" s="8"/>
+    </row>
+    <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D680" s="8"/>
+    </row>
+    <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D681" s="8"/>
+    </row>
+    <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D682" s="8"/>
+    </row>
+    <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D683" s="8"/>
+    </row>
+    <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D684" s="8"/>
+    </row>
+    <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D685" s="8"/>
+    </row>
+    <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D686" s="8"/>
+    </row>
+    <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D687" s="8"/>
+    </row>
+    <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D688" s="8"/>
+    </row>
+    <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D689" s="8"/>
+    </row>
+    <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D690" s="8"/>
+    </row>
+    <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D691" s="8"/>
+    </row>
+    <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D692" s="8"/>
+    </row>
+    <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D693" s="8"/>
+    </row>
+    <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D694" s="8"/>
+    </row>
+    <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D695" s="8"/>
+    </row>
+    <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D696" s="8"/>
+    </row>
+    <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D697" s="8"/>
+    </row>
+    <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D698" s="8"/>
+    </row>
+    <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D699" s="8"/>
+    </row>
+    <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D700" s="8"/>
+    </row>
+    <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D701" s="8"/>
+    </row>
+    <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D702" s="8"/>
+    </row>
+    <row r="703" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D703" s="8"/>
+    </row>
+    <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D704" s="8"/>
+    </row>
+    <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D705" s="8"/>
+    </row>
+    <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D706" s="8"/>
+    </row>
+    <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D707" s="8"/>
+    </row>
+    <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D708" s="8"/>
+    </row>
+    <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D709" s="8"/>
+    </row>
+    <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D710" s="8"/>
+    </row>
+    <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D711" s="8"/>
+    </row>
+    <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D712" s="8"/>
+    </row>
+    <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D713" s="8"/>
+    </row>
+    <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D714" s="8"/>
+    </row>
+    <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D715" s="8"/>
+    </row>
+    <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D716" s="8"/>
+    </row>
+    <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D717" s="8"/>
+    </row>
+    <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D718" s="8"/>
+    </row>
+    <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D719" s="8"/>
+    </row>
+    <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D720" s="8"/>
+    </row>
+    <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D721" s="8"/>
+    </row>
+    <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D722" s="8"/>
+    </row>
+    <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D723" s="8"/>
+    </row>
+    <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D724" s="8"/>
+    </row>
+    <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D725" s="8"/>
+    </row>
+    <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D726" s="8"/>
+    </row>
+    <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D727" s="8"/>
+    </row>
+    <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D728" s="8"/>
+    </row>
+    <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D729" s="8"/>
+    </row>
+    <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D730" s="8"/>
+    </row>
+    <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D731" s="8"/>
+    </row>
+    <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D732" s="8"/>
+    </row>
+    <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D733" s="8"/>
+    </row>
+    <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D734" s="8"/>
+    </row>
+    <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D735" s="8"/>
+    </row>
+    <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D736" s="8"/>
+    </row>
+    <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D737" s="8"/>
+    </row>
+    <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D738" s="8"/>
+    </row>
+    <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D739" s="8"/>
+    </row>
+    <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D740" s="8"/>
+    </row>
+    <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D741" s="8"/>
+    </row>
+    <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D742" s="8"/>
+    </row>
+    <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D743" s="8"/>
+    </row>
+    <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D744" s="8"/>
+    </row>
+    <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D745" s="8"/>
+    </row>
+    <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D746" s="8"/>
+    </row>
+    <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D747" s="8"/>
+    </row>
+    <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D748" s="8"/>
+    </row>
+    <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D749" s="8"/>
+    </row>
+    <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D750" s="8"/>
+    </row>
+    <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D751" s="8"/>
+    </row>
+    <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D752" s="8"/>
+    </row>
+    <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D753" s="8"/>
+    </row>
+    <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D754" s="8"/>
+    </row>
+    <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D755" s="8"/>
+    </row>
+    <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D756" s="8"/>
+    </row>
+    <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D757" s="8"/>
+    </row>
+    <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D758" s="8"/>
+    </row>
+    <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D759" s="8"/>
+    </row>
+    <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D760" s="8"/>
+    </row>
+    <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D761" s="8"/>
+    </row>
+    <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D762" s="8"/>
+    </row>
+    <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D763" s="8"/>
+    </row>
+    <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D764" s="8"/>
+    </row>
+    <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D765" s="8"/>
+    </row>
+    <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D766" s="8"/>
+    </row>
+    <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D767" s="8"/>
+    </row>
+    <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D768" s="8"/>
+    </row>
+    <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D769" s="8"/>
+    </row>
+    <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D770" s="8"/>
+    </row>
+    <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D771" s="8"/>
+    </row>
+    <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D772" s="8"/>
+    </row>
+    <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D773" s="8"/>
+    </row>
+    <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D774" s="8"/>
+    </row>
+    <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D775" s="8"/>
+    </row>
+    <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D776" s="8"/>
+    </row>
+    <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D777" s="8"/>
+    </row>
+    <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D778" s="8"/>
+    </row>
+    <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D779" s="8"/>
+    </row>
+    <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D780" s="8"/>
+    </row>
+    <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D781" s="8"/>
+    </row>
+    <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D782" s="8"/>
+    </row>
+    <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D783" s="8"/>
+    </row>
+    <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D784" s="8"/>
+    </row>
+    <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D785" s="8"/>
+    </row>
+    <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D786" s="8"/>
+    </row>
+    <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D787" s="8"/>
+    </row>
+    <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D788" s="8"/>
+    </row>
+    <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D789" s="8"/>
+    </row>
+    <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D790" s="8"/>
+    </row>
+    <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D791" s="8"/>
+    </row>
+    <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D792" s="8"/>
+    </row>
+    <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D793" s="8"/>
+    </row>
+    <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D794" s="8"/>
+    </row>
+    <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D795" s="8"/>
+    </row>
+    <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D796" s="8"/>
+    </row>
+    <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D797" s="8"/>
+    </row>
+    <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D798" s="8"/>
+    </row>
+    <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D799" s="8"/>
+    </row>
+    <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D800" s="8"/>
+    </row>
+    <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D801" s="8"/>
+    </row>
+    <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D802" s="8"/>
+    </row>
+    <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D803" s="8"/>
+    </row>
+    <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D804" s="8"/>
+    </row>
+    <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D805" s="8"/>
+    </row>
+    <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D806" s="8"/>
+    </row>
+    <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D807" s="8"/>
+    </row>
+    <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D808" s="8"/>
+    </row>
+    <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D809" s="8"/>
+    </row>
+    <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D810" s="8"/>
+    </row>
+    <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D811" s="8"/>
+    </row>
+    <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D812" s="8"/>
+    </row>
+    <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D813" s="8"/>
+    </row>
+    <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D814" s="8"/>
+    </row>
+    <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D815" s="8"/>
+    </row>
+    <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D816" s="8"/>
+    </row>
+    <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D817" s="8"/>
+    </row>
+    <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D818" s="8"/>
+    </row>
+    <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D819" s="8"/>
+    </row>
+    <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D820" s="8"/>
+    </row>
+    <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D821" s="8"/>
+    </row>
+    <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D822" s="8"/>
+    </row>
+    <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D823" s="8"/>
+    </row>
+    <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D824" s="8"/>
+    </row>
+    <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D825" s="8"/>
+    </row>
+    <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D826" s="8"/>
+    </row>
+    <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D827" s="8"/>
+    </row>
+    <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D828" s="8"/>
+    </row>
+    <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D829" s="8"/>
+    </row>
+    <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D830" s="8"/>
+    </row>
+    <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D831" s="8"/>
+    </row>
+    <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D832" s="8"/>
+    </row>
+    <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D833" s="8"/>
+    </row>
+    <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D834" s="8"/>
+    </row>
+    <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D835" s="8"/>
+    </row>
+    <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D836" s="8"/>
+    </row>
+    <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D837" s="8"/>
+    </row>
+    <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D838" s="8"/>
+    </row>
+    <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D839" s="8"/>
+    </row>
+    <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D840" s="8"/>
+    </row>
+    <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D841" s="8"/>
+    </row>
+    <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D842" s="8"/>
+    </row>
+    <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D843" s="8"/>
+    </row>
+    <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D844" s="8"/>
+    </row>
+    <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D845" s="8"/>
+    </row>
+    <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D846" s="8"/>
+    </row>
+    <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D847" s="8"/>
+    </row>
+    <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D848" s="8"/>
+    </row>
+    <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D849" s="8"/>
+    </row>
+    <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D850" s="8"/>
+    </row>
+    <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D851" s="8"/>
+    </row>
+    <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D852" s="8"/>
+    </row>
+    <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D853" s="8"/>
+    </row>
+    <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D854" s="8"/>
+    </row>
+    <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D855" s="8"/>
+    </row>
+    <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D856" s="8"/>
+    </row>
+    <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D857" s="8"/>
+    </row>
+    <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D858" s="8"/>
+    </row>
+    <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D859" s="8"/>
+    </row>
+    <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D860" s="8"/>
+    </row>
+    <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D861" s="8"/>
+    </row>
+    <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D862" s="8"/>
+    </row>
+    <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D863" s="8"/>
+    </row>
+    <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D864" s="8"/>
+    </row>
+    <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D865" s="8"/>
+    </row>
+    <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D866" s="8"/>
+    </row>
+    <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D867" s="8"/>
+    </row>
+    <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D868" s="8"/>
+    </row>
+    <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D869" s="8"/>
+    </row>
+    <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D870" s="8"/>
+    </row>
+    <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D871" s="8"/>
+    </row>
+    <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D872" s="8"/>
+    </row>
+    <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D873" s="8"/>
+    </row>
+    <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D874" s="8"/>
+    </row>
+    <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D875" s="8"/>
+    </row>
+    <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D876" s="8"/>
+    </row>
+    <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D877" s="8"/>
+    </row>
+    <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D878" s="8"/>
+    </row>
+    <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D879" s="8"/>
+    </row>
+    <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D880" s="8"/>
+    </row>
+    <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D881" s="8"/>
+    </row>
+    <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D882" s="8"/>
+    </row>
+    <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D883" s="8"/>
+    </row>
+    <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D884" s="8"/>
+    </row>
+    <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D885" s="8"/>
+    </row>
+    <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D886" s="8"/>
+    </row>
+    <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D887" s="8"/>
+    </row>
+    <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D888" s="8"/>
+    </row>
+    <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D889" s="8"/>
+    </row>
+    <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D890" s="8"/>
+    </row>
+    <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D891" s="8"/>
+    </row>
+    <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D892" s="8"/>
+    </row>
+    <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D893" s="8"/>
+    </row>
+    <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D894" s="8"/>
+    </row>
+    <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D895" s="8"/>
+    </row>
+    <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D896" s="8"/>
+    </row>
+    <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D897" s="8"/>
+    </row>
+    <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D898" s="8"/>
+    </row>
+    <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D899" s="8"/>
+    </row>
+    <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D900" s="8"/>
+    </row>
+    <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D901" s="8"/>
+    </row>
+    <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D902" s="8"/>
+    </row>
+    <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D903" s="8"/>
+    </row>
+    <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D904" s="8"/>
+    </row>
+    <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D905" s="8"/>
+    </row>
+    <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D906" s="8"/>
+    </row>
+    <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D907" s="8"/>
+    </row>
+    <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D908" s="8"/>
+    </row>
+    <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D909" s="8"/>
+    </row>
+    <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D910" s="8"/>
+    </row>
+    <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D911" s="8"/>
+    </row>
+    <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D912" s="8"/>
+    </row>
+    <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D913" s="8"/>
+    </row>
+    <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D914" s="8"/>
+    </row>
+    <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D915" s="8"/>
+    </row>
+    <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D916" s="8"/>
+    </row>
+    <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D917" s="8"/>
+    </row>
+    <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D918" s="8"/>
+    </row>
+    <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D919" s="8"/>
+    </row>
+    <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D920" s="8"/>
+    </row>
+    <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D921" s="8"/>
+    </row>
+    <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D922" s="8"/>
+    </row>
+    <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D923" s="8"/>
+    </row>
+    <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D924" s="8"/>
+    </row>
+    <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D925" s="8"/>
+    </row>
+    <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D926" s="8"/>
+    </row>
+    <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D927" s="8"/>
+    </row>
+    <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D928" s="8"/>
+    </row>
+    <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D929" s="8"/>
+    </row>
+    <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D930" s="8"/>
+    </row>
+    <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D931" s="8"/>
+    </row>
+    <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D932" s="8"/>
+    </row>
+    <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D933" s="8"/>
+    </row>
+    <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D934" s="8"/>
+    </row>
+    <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D935" s="8"/>
+    </row>
+    <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D936" s="8"/>
+    </row>
+    <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D937" s="8"/>
+    </row>
+    <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D938" s="8"/>
+    </row>
+    <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D939" s="8"/>
+    </row>
+    <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D940" s="8"/>
+    </row>
+    <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D941" s="8"/>
+    </row>
+    <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D942" s="8"/>
+    </row>
+    <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D943" s="8"/>
+    </row>
+    <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D944" s="8"/>
+    </row>
+    <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D945" s="8"/>
+    </row>
+    <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D946" s="8"/>
+    </row>
+    <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D947" s="8"/>
+    </row>
+    <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D948" s="8"/>
+    </row>
+    <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D949" s="8"/>
+    </row>
+    <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D950" s="8"/>
+    </row>
+    <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D951" s="8"/>
+    </row>
+    <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D952" s="8"/>
+    </row>
+    <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D953" s="8"/>
+    </row>
+    <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D954" s="8"/>
+    </row>
+    <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D955" s="8"/>
+    </row>
+    <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D956" s="8"/>
+    </row>
+    <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D957" s="8"/>
+    </row>
+    <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D958" s="8"/>
+    </row>
+    <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D959" s="8"/>
+    </row>
+    <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D960" s="8"/>
+    </row>
+    <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D961" s="8"/>
+    </row>
+    <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D962" s="8"/>
+    </row>
+    <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D963" s="8"/>
+    </row>
+    <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D964" s="8"/>
+    </row>
+    <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D965" s="8"/>
+    </row>
+    <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D966" s="8"/>
+    </row>
+    <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D967" s="8"/>
+    </row>
+    <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D968" s="8"/>
+    </row>
+    <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D969" s="8"/>
+    </row>
+    <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D970" s="8"/>
+    </row>
+    <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D971" s="8"/>
+    </row>
+    <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D972" s="8"/>
+    </row>
+    <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D973" s="8"/>
+    </row>
+    <row r="974" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D974" s="8"/>
+    </row>
+    <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D975" s="8"/>
+    </row>
+    <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D976" s="8"/>
+    </row>
+    <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D977" s="8"/>
+    </row>
+    <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D978" s="8"/>
+    </row>
+    <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D979" s="8"/>
+    </row>
+    <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D980" s="8"/>
+    </row>
+    <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D981" s="8"/>
+    </row>
+    <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D982" s="8"/>
+    </row>
+    <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D983" s="8"/>
+    </row>
+    <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D984" s="8"/>
+    </row>
+    <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D985" s="8"/>
+    </row>
+    <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D986" s="8"/>
+    </row>
+    <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D987" s="8"/>
+    </row>
+    <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D988" s="8"/>
+    </row>
+    <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D989" s="8"/>
+    </row>
+    <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D990" s="8"/>
+    </row>
+    <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D991" s="8"/>
+    </row>
+    <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D992" s="8"/>
+    </row>
+    <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D993" s="8"/>
+    </row>
+    <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D994" s="8"/>
+    </row>
+    <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D995" s="8"/>
+    </row>
+    <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D996" s="8"/>
+    </row>
+    <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D997" s="8"/>
+    </row>
+    <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D998" s="24"/>
+    </row>
+    <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D999" s="24"/>
+    </row>
+    <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D1000" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A6:B8"/>
+    <mergeCell ref="A9:B10"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF81D41A"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B164"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="17.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="20.22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="26" t="n">
+        <v>23</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="26" t="n">
+        <v>33</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="26" t="n">
+        <v>39</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="26" t="n">
+        <v>41</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="26" t="n">
+        <v>42</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="26" t="n">
+        <v>46</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="26" t="n">
+        <v>47</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="26" t="n">
+        <v>49</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="26" t="n">
+        <v>52</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="26" t="n">
+        <v>53</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="26" t="n">
+        <v>54</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="26" t="n">
+        <v>56</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="26" t="n">
+        <v>58</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="26" t="n">
+        <v>61</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="26" t="n">
+        <v>63</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="26" t="n">
+        <v>64</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="26" t="n">
+        <v>65</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="26" t="n">
+        <v>66</v>
+      </c>
+      <c r="B55" s="26" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="26" t="n">
+        <v>67</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="26" t="n">
+        <v>68</v>
+      </c>
+      <c r="B57" s="26" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="B58" s="26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="26" t="n">
+        <v>71</v>
+      </c>
+      <c r="B59" s="26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="26" t="n">
+        <v>72</v>
+      </c>
+      <c r="B60" s="26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="26" t="n">
+        <v>73</v>
+      </c>
+      <c r="B61" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="B62" s="26" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="B63" s="26" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="B64" s="26" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="26" t="n">
+        <v>77</v>
+      </c>
+      <c r="B65" s="26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="B66" s="26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="26" t="n">
+        <v>79</v>
+      </c>
+      <c r="B67" s="26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="26" t="n">
+        <v>81</v>
+      </c>
+      <c r="B68" s="26" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="26" t="n">
+        <v>83</v>
+      </c>
+      <c r="B70" s="26" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="B71" s="26" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="26" t="n">
+        <v>85</v>
+      </c>
+      <c r="B72" s="26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="B73" s="26" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="26" t="n">
+        <v>87</v>
+      </c>
+      <c r="B74" s="26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="B75" s="26" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="26" t="n">
+        <v>89</v>
+      </c>
+      <c r="B76" s="26" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="B77" s="26" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="26" t="n">
+        <v>94</v>
+      </c>
+      <c r="B78" s="26" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="26" t="n">
+        <v>95</v>
+      </c>
+      <c r="B79" s="26" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="26" t="n">
+        <v>96</v>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="26" t="n">
+        <v>97</v>
+      </c>
+      <c r="B81" s="26" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="26" t="n">
+        <v>98</v>
+      </c>
+      <c r="B82" s="26" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="B83" s="26" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="26" t="n">
+        <v>207</v>
+      </c>
+      <c r="B84" s="26" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="26" t="n">
+        <v>215</v>
+      </c>
+      <c r="B85" s="26" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="26" t="n">
+        <v>217</v>
+      </c>
+      <c r="B86" s="26" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="26" t="n">
+        <v>219</v>
+      </c>
+      <c r="B87" s="26" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="26" t="n">
+        <v>235</v>
+      </c>
+      <c r="B88" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="26" t="n">
+        <v>236</v>
+      </c>
+      <c r="B89" s="26" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="26" t="n">
+        <v>237</v>
+      </c>
+      <c r="B90" s="26" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="26" t="n">
+        <v>238</v>
+      </c>
+      <c r="B91" s="26" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="26" t="n">
+        <v>243</v>
+      </c>
+      <c r="B92" s="26" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="26" t="n">
+        <v>244</v>
+      </c>
+      <c r="B93" s="26" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="26" t="n">
+        <v>245</v>
+      </c>
+      <c r="B94" s="26" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="26" t="n">
+        <v>253</v>
+      </c>
+      <c r="B95" s="26" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="26" t="n">
+        <v>255</v>
+      </c>
+      <c r="B96" s="26" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="26" t="n">
+        <v>256</v>
+      </c>
+      <c r="B97" s="26" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="26" t="n">
+        <v>257</v>
+      </c>
+      <c r="B98" s="26" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="26" t="n">
+        <v>258</v>
+      </c>
+      <c r="B99" s="26" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="26" t="n">
+        <v>264</v>
+      </c>
+      <c r="B100" s="26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="26" t="n">
+        <v>268</v>
+      </c>
+      <c r="B101" s="26" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="26" t="n">
+        <v>273</v>
+      </c>
+      <c r="B102" s="26" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="26" t="n">
+        <v>275</v>
+      </c>
+      <c r="B103" s="26" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="26" t="n">
+        <v>276</v>
+      </c>
+      <c r="B104" s="26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="26" t="n">
+        <v>277</v>
+      </c>
+      <c r="B105" s="26" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="26" t="n">
+        <v>278</v>
+      </c>
+      <c r="B106" s="26" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="26" t="n">
+        <v>279</v>
+      </c>
+      <c r="B107" s="26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="26" t="n">
+        <v>281</v>
+      </c>
+      <c r="B108" s="26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="26" t="n">
+        <v>282</v>
+      </c>
+      <c r="B109" s="26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="26" t="n">
+        <v>283</v>
+      </c>
+      <c r="B110" s="26" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="26" t="n">
+        <v>289</v>
+      </c>
+      <c r="B111" s="26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="26" t="n">
+        <v>292</v>
+      </c>
+      <c r="B112" s="26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="26" t="n">
+        <v>293</v>
+      </c>
+      <c r="B113" s="26" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="26" t="n">
+        <v>294</v>
+      </c>
+      <c r="B114" s="26" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="26" t="n">
+        <v>299</v>
+      </c>
+      <c r="B115" s="26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="26" t="n">
+        <v>307</v>
+      </c>
+      <c r="B116" s="26" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="26" t="n">
+        <v>315</v>
+      </c>
+      <c r="B117" s="26" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="26" t="n">
+        <v>317</v>
+      </c>
+      <c r="B118" s="26" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="26" t="n">
+        <v>319</v>
+      </c>
+      <c r="B119" s="26" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="26" t="n">
+        <v>335</v>
+      </c>
+      <c r="B120" s="26" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="26" t="n">
+        <v>336</v>
+      </c>
+      <c r="B121" s="26" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="26" t="n">
+        <v>337</v>
+      </c>
+      <c r="B122" s="26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="26" t="n">
+        <v>344</v>
+      </c>
+      <c r="B123" s="26" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="26" t="n">
+        <v>355</v>
+      </c>
+      <c r="B124" s="26" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="26" t="n">
+        <v>356</v>
+      </c>
+      <c r="B125" s="26" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="26" t="n">
+        <v>357</v>
+      </c>
+      <c r="B126" s="26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="26" t="n">
+        <v>364</v>
+      </c>
+      <c r="B127" s="26" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="26" t="n">
+        <v>373</v>
+      </c>
+      <c r="B128" s="26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="26" t="n">
+        <v>376</v>
+      </c>
+      <c r="B129" s="26" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="26" t="n">
+        <v>377</v>
+      </c>
+      <c r="B130" s="26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="26" t="n">
+        <v>378</v>
+      </c>
+      <c r="B131" s="26" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="26" t="n">
+        <v>389</v>
+      </c>
+      <c r="B132" s="26" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="26" t="n">
+        <v>392</v>
+      </c>
+      <c r="B133" s="26" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="26" t="n">
+        <v>395</v>
+      </c>
+      <c r="B134" s="26" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="26" t="n">
+        <v>399</v>
+      </c>
+      <c r="B135" s="26" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="26" t="n">
+        <v>415</v>
+      </c>
+      <c r="B136" s="26" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="26" t="n">
+        <v>435</v>
+      </c>
+      <c r="B137" s="26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="26" t="n">
+        <v>436</v>
+      </c>
+      <c r="B138" s="26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="26" t="n">
+        <v>455</v>
+      </c>
+      <c r="B139" s="26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="26" t="n">
+        <v>456</v>
+      </c>
+      <c r="B140" s="26" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="26" t="n">
+        <v>457</v>
+      </c>
+      <c r="B141" s="26" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="26" t="n">
+        <v>464</v>
+      </c>
+      <c r="B142" s="26" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="26" t="n">
+        <v>469</v>
+      </c>
+      <c r="B143" s="26" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="26" t="n">
+        <v>476</v>
+      </c>
+      <c r="B144" s="26" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="26" t="n">
+        <v>478</v>
+      </c>
+      <c r="B145" s="26" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="26" t="n">
+        <v>489</v>
+      </c>
+      <c r="B146" s="26" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="26" t="n">
+        <v>495</v>
+      </c>
+      <c r="B147" s="26" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="26" t="n">
+        <v>499</v>
+      </c>
+      <c r="B148" s="26" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="26" t="n">
+        <v>515</v>
+      </c>
+      <c r="B149" s="26" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="26" t="n">
+        <v>557</v>
+      </c>
+      <c r="B150" s="26" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="26" t="n">
+        <v>569</v>
+      </c>
+      <c r="B151" s="26" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="26" t="n">
+        <v>576</v>
+      </c>
+      <c r="B152" s="26" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="26" t="n">
+        <v>578</v>
+      </c>
+      <c r="B153" s="26" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="26" t="n">
+        <v>595</v>
+      </c>
+      <c r="B154" s="26" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="26" t="n">
+        <v>599</v>
+      </c>
+      <c r="B155" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="26" t="n">
+        <v>657</v>
+      </c>
+      <c r="B156" s="26" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="26" t="n">
+        <v>676</v>
+      </c>
+      <c r="B157" s="26" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="26" t="n">
+        <v>678</v>
+      </c>
+      <c r="B158" s="26" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="26" t="n">
+        <v>757</v>
+      </c>
+      <c r="B159" s="26" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="26" t="n">
+        <v>776</v>
+      </c>
+      <c r="B160" s="26" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="26" t="n">
+        <v>778</v>
+      </c>
+      <c r="B161" s="26" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="26" t="n">
+        <v>857</v>
+      </c>
+      <c r="B162" s="26" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="26" t="n">
+        <v>858</v>
+      </c>
+      <c r="B163" s="26" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="26" t="n">
+        <v>957</v>
+      </c>
+      <c r="B164" s="26" t="s">
+        <v>215</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF81D41A"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B53"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="17.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="20.22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="26" t="n">
+        <v>33</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="26" t="n">
+        <v>39</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="26" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="26" t="n">
+        <v>52</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="26" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="26" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="26" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="26" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="26" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>269</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>